--- a/BWI/bestwine_output/bestwine_Dominican Rep.xlsx
+++ b/BWI/bestwine_output/bestwine_Dominican Rep.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA40"/>
+  <dimension ref="A1:AA43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -4804,6 +4804,309 @@
       <c r="Z40" s="4" t="inlineStr"/>
       <c r="AA40" s="4" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>27 Calle Clarín</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>https://superbravo.com.do</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>info@bravo.com.do</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-740-5009</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bravosa/</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SupermercadosBravo/</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercadosbravo</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@supermercadosbravo.</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>Quilvio Ernesto</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>Retail Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/quilvio-ernesto-castillo-lapaz-8b7561b8/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>27 Calle Clarín</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>https://superbravo.com.do</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>info@bravo.com.do</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-740-5009</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bravosa/</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SupermercadosBravo/</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercadosbravo</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@supermercadosbravo.</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>Licelott Solano</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/licelott-solano-89671a10b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>27 Calle Clarín</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>https://superbravo.com.do</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>info@bravo.com.do</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-740-5009</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bravosa/</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SupermercadosBravo/</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercadosbravo</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@supermercadosbravo.</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>Harold Guzman</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Planner</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/harold-guzman-2a5771144/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Dominican Rep.xlsx
+++ b/BWI/bestwine_output/bestwine_Dominican Rep.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA43"/>
+  <dimension ref="A1:AA49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -5107,6 +5107,648 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>116567</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Ave. 27 De Febrero Esq. Winston Churchill</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>01011</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://plazalama.com.do</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>tiendaenlinea@plazalama.com</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-274-5262</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>1929</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>101171111</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/plaza-lama/</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/plazalama</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/plazalama/</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PlazaLamaSA</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>Elizabeth Altagracia Vásquez Santana</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>Import Manager</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elizabeth-altagracia-v%C3%A1squez-santana-b433a42a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>116567</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Ave. 27 De Febrero Esq. Winston Churchill</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>01011</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>https://plazalama.com.do</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>tiendaenlinea@plazalama.com</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-274-5262</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>1929</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>101171111</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/plaza-lama/</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/plazalama</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/plazalama/</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PlazaLamaSA</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>Manuel Luciano Lora</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/manuel-luciano-lora-2b31381b8/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>116567</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Ave. 27 De Febrero Esq. Winston Churchill</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>01011</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>https://plazalama.com.do</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>tiendaenlinea@plazalama.com</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-274-5262</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>1929</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>101171111</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/plaza-lama/</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/plazalama</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/plazalama/</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PlazaLamaSA</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>Sarah Fiallo Dipp</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Purchasing Manager </t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sarah-fiallo-dipp-85861396/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>27 Calle Clarín</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>https://superbravo.com.do</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>info@bravo.com.do</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-740-5009</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bravosa/</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SupermercadosBravo/</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercadosbravo</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@supermercadosbravo.</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>Quilvio Ernesto</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>Retail Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/quilvio-ernesto-castillo-lapaz-8b7561b8/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>27 Calle Clarín</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>https://superbravo.com.do</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>info@bravo.com.do</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-740-5009</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bravosa/</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SupermercadosBravo/</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercadosbravo</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@supermercadosbravo.</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>Licelott Solano</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/licelott-solano-89671a10b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>27 Calle Clarín</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>https://superbravo.com.do</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>info@bravo.com.do</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-740-5009</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bravosa/</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SupermercadosBravo/</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercadosbravo</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@supermercadosbravo.</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>Harold Guzman</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Planner</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/harold-guzman-2a5771144/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Dominican Rep.xlsx
+++ b/BWI/bestwine_output/bestwine_Dominican Rep.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA49"/>
+  <dimension ref="A1:AA55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -5749,6 +5749,648 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>116567</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Ave. 27 De Febrero Esq. Winston Churchill</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>01011</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>https://plazalama.com.do</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>tiendaenlinea@plazalama.com</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-274-5262</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>1929</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>101171111</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/plaza-lama/</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/plazalama</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/plazalama/</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PlazaLamaSA</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>Elizabeth Altagracia Vásquez Santana</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>Import Manager</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elizabeth-altagracia-v%C3%A1squez-santana-b433a42a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>116567</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Ave. 27 De Febrero Esq. Winston Churchill</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>01011</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>https://plazalama.com.do</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>tiendaenlinea@plazalama.com</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-274-5262</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>1929</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>101171111</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/plaza-lama/</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/plazalama</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/plazalama/</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PlazaLamaSA</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>Manuel Luciano Lora</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/manuel-luciano-lora-2b31381b8/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>116567</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Ave. 27 De Febrero Esq. Winston Churchill</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>01011</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>https://plazalama.com.do</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>tiendaenlinea@plazalama.com</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-274-5262</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>1929</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>101171111</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/plaza-lama/</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/plazalama</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/plazalama/</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PlazaLamaSA</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>Sarah Fiallo Dipp</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Purchasing Manager </t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr"/>
+      <c r="Z52" s="2" t="inlineStr"/>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sarah-fiallo-dipp-85861396/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>27 Calle Clarín</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>https://superbravo.com.do</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>info@bravo.com.do</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-740-5009</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bravosa/</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SupermercadosBravo/</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercadosbravo</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@supermercadosbravo.</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>Quilvio Ernesto</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>Retail Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr"/>
+      <c r="Z53" s="2" t="inlineStr"/>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/quilvio-ernesto-castillo-lapaz-8b7561b8/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>27 Calle Clarín</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>https://superbravo.com.do</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>info@bravo.com.do</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-740-5009</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bravosa/</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SupermercadosBravo/</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercadosbravo</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@supermercadosbravo.</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>Licelott Solano</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr"/>
+      <c r="Z54" s="2" t="inlineStr"/>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/licelott-solano-89671a10b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>27 Calle Clarín</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>https://superbravo.com.do</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>info@bravo.com.do</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-740-5009</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bravosa/</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SupermercadosBravo/</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercadosbravo</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@supermercadosbravo.</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>Harold Guzman</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Planner</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr"/>
+      <c r="Z55" s="2" t="inlineStr"/>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/harold-guzman-2a5771144/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Dominican Rep.xlsx
+++ b/BWI/bestwine_output/bestwine_Dominican Rep.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA55"/>
+  <dimension ref="A1:AA61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -6391,6 +6391,648 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>116567</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Ave. 27 De Febrero Esq. Winston Churchill</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>01011</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>https://plazalama.com.do</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>tiendaenlinea@plazalama.com</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-274-5262</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>1929</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>101171111</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/plaza-lama/</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/plazalama</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/plazalama/</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PlazaLamaSA</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>Elizabeth Altagracia Vásquez Santana</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>Import Manager</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Z56" s="2" t="inlineStr"/>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elizabeth-altagracia-v%C3%A1squez-santana-b433a42a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>116567</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Ave. 27 De Febrero Esq. Winston Churchill</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>01011</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>https://plazalama.com.do</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>tiendaenlinea@plazalama.com</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-274-5262</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>1929</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>101171111</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/plaza-lama/</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/plazalama</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/plazalama/</t>
+        </is>
+      </c>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PlazaLamaSA</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>Sarah Fiallo Dipp</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Purchasing Manager </t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr"/>
+      <c r="Z57" s="2" t="inlineStr"/>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sarah-fiallo-dipp-85861396/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>116567</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Ave. 27 De Febrero Esq. Winston Churchill</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>01011</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>https://plazalama.com.do</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>tiendaenlinea@plazalama.com</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-274-5262</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>1929</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>101171111</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/plaza-lama/</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/plazalama</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/plazalama/</t>
+        </is>
+      </c>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PlazaLamaSA</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>Manuel Luciano Lora</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr"/>
+      <c r="Z58" s="2" t="inlineStr"/>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/manuel-luciano-lora-2b31381b8/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>27 Calle Clarín</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>https://superbravo.com.do</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>info@bravo.com.do</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-740-5009</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bravosa/</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SupermercadosBravo/</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercadosbravo</t>
+        </is>
+      </c>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@supermercadosbravo.</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>Quilvio Ernesto</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>Retail Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr"/>
+      <c r="Z59" s="2" t="inlineStr"/>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/quilvio-ernesto-castillo-lapaz-8b7561b8/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>27 Calle Clarín</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>https://superbravo.com.do</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>info@bravo.com.do</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-740-5009</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bravosa/</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SupermercadosBravo/</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercadosbravo</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@supermercadosbravo.</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>Licelott Solano</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr"/>
+      <c r="Z60" s="2" t="inlineStr"/>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/licelott-solano-89671a10b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>27 Calle Clarín</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>https://superbravo.com.do</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>info@bravo.com.do</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-740-5009</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bravosa/</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SupermercadosBravo/</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercadosbravo</t>
+        </is>
+      </c>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@supermercadosbravo.</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>Harold Guzman</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Planner</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr"/>
+      <c r="Z61" s="2" t="inlineStr"/>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/harold-guzman-2a5771144/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Dominican Rep.xlsx
+++ b/BWI/bestwine_output/bestwine_Dominican Rep.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA61"/>
+  <dimension ref="A1:AA67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7033,6 +7033,648 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>116567</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Ave. 27 De Febrero Esq. Winston Churchill</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>01011</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>https://plazalama.com.do</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>tiendaenlinea@plazalama.com</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-274-5262</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>1929</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>101171111</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/plaza-lama/</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/plazalama</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/plazalama/</t>
+        </is>
+      </c>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PlazaLamaSA</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>Elizabeth Altagracia Vásquez Santana</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>Import Manager</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr"/>
+      <c r="Z62" s="2" t="inlineStr"/>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elizabeth-altagracia-v%C3%A1squez-santana-b433a42a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>116567</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Ave. 27 De Febrero Esq. Winston Churchill</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>01011</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>https://plazalama.com.do</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>tiendaenlinea@plazalama.com</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-274-5262</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>1929</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>101171111</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/plaza-lama/</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/plazalama</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/plazalama/</t>
+        </is>
+      </c>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PlazaLamaSA</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>Sarah Fiallo Dipp</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Purchasing Manager </t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr"/>
+      <c r="Z63" s="2" t="inlineStr"/>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sarah-fiallo-dipp-85861396/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Plaza Lama, S.a.</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>116567</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Ave. 27 De Febrero Esq. Winston Churchill</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>01011</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>https://plazalama.com.do</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>tiendaenlinea@plazalama.com</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-274-5262</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>1929</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>101171111</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/plaza-lama/</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/plazalama</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/plazalama/</t>
+        </is>
+      </c>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PlazaLamaSA</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>Manuel Luciano Lora</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr"/>
+      <c r="Z64" s="2" t="inlineStr"/>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/manuel-luciano-lora-2b31381b8/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>27 Calle Clarín</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>https://superbravo.com.do</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>info@bravo.com.do</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-740-5009</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bravosa/</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SupermercadosBravo/</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercadosbravo</t>
+        </is>
+      </c>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@supermercadosbravo.</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>Quilvio Ernesto</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>Retail Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr"/>
+      <c r="Z65" s="2" t="inlineStr"/>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/quilvio-ernesto-castillo-lapaz-8b7561b8/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>27 Calle Clarín</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>https://superbravo.com.do</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>info@bravo.com.do</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-740-5009</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bravosa/</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SupermercadosBravo/</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercadosbravo</t>
+        </is>
+      </c>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@supermercadosbravo.</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>Licelott Solano</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr"/>
+      <c r="Z66" s="2" t="inlineStr"/>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/licelott-solano-89671a10b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Bravo</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Dominican Rep.</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Nacional de Guzman</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>27 Calle Clarín</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>https://superbravo.com.do</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>info@bravo.com.do</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>+1 809-740-5009</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr"/>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bravosa/</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SupermercadosBravo/</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercadosbravo</t>
+        </is>
+      </c>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@supermercadosbravo.</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>Harold Guzman</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Planner</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr"/>
+      <c r="Z67" s="2" t="inlineStr"/>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/harold-guzman-2a5771144/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
